--- a/testakten/unfallversicherung-arbeitsunfall-lagerleiter-sturz-trier/xlsx/fehlzeiten_uebersicht_2016_2026.xlsx
+++ b/testakten/unfallversicherung-arbeitsunfall-lagerleiter-sturz-trier/xlsx/fehlzeiten_uebersicht_2016_2026.xlsx
@@ -440,7 +440,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fehlzeitenuebersicht Karsten Moeller, 2016 bis 2026</t>
+          <t>Fehlzeitenübersicht Karsten Möller, 2016 bis 2026</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Keine Fehltage, Vorsorgeuntersuchung uneingeschraenkt tauglich</t>
+          <t>Keine Fehltage, Vorsorgeuntersuchung uneingeschränktt tauglich</t>
         </is>
       </c>
     </row>
